--- a/output/2026-09-20_09_Croazia_Vukovarsko-srijemska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_09_Croazia_Vukovarsko-srijemska_ATEX_Equipment-Services.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Confermato: sito ufficiale con sezione dedicata 'ATEX Equipment', personale certificato CompEx.</t>
+          <t>Confermato: sito ufficiale con sezione dedicata 'ATEX Equipment', personale certificato CompEx. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Confermato: filiale croata del gruppo multinazionale SMC, pagina prodotti ATEX dedicata sul sito.</t>
+          <t>Confermato: filiale croata del gruppo multinazionale SMC, pagina prodotti ATEX dedicata sul sito. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">

--- a/output/2026-09-20_09_Croazia_Vukovarsko-srijemska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_09_Croazia_Vukovarsko-srijemska_ATEX_Equipment-Services.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-20_09_Croazia_Vukovarsko-srijemska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_09_Croazia_Vukovarsko-srijemska_ATEX_Equipment-Services.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Confermata esistenza e sede; sito ufficiale mostra linea prodotti ATEX (es. ventilatore elettrico ESX230, SAX350). Azienda certificata ISO 9001. Email generica non reperita.</t>
+          <t>Confermata esistenza e sede; sito ufficiale mostra linea prodotti ATEX (es. ventilatore elettrico ESX230, SAX350). Azienda certificata ISO 9001. Email generica non reperita. [DUPLICATO — vedi anche: 2026-09-07_22_Croazia_Zagrebacka_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Confermata su registri camerali (fininfo.hr, companywall.hr) e sito ufficiale, sezione dedicata 'Protueksplozijska (Ex) zaštita'. Attiva dal 2000.</t>
+          <t>Confermata su registri camerali (fininfo.hr, companywall.hr) e sito ufficiale, sezione dedicata 'Protueksplozijska (Ex) zaštita'. Attiva dal 2000. [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Confermato: Notified Body 2829, succeduto a Ex-Agencija/S-Komisija dal 2019. Servizio di certificazione, non distributore di prodotti fisici.</t>
+          <t>Confermato: Notified Body 2829, succeduto a Ex-Agencija/S-Komisija dal 2019. Servizio di certificazione, non distributore di prodotti fisici. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Confermato su registri camerali e sito ufficiale (pagina Kontakt).</t>
+          <t>Confermato su registri camerali e sito ufficiale (pagina Kontakt). [DUPLICATO — vedi anche: 2026-09-13_23_Croazia_Primorsko-goranska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
